--- a/src/test/resources/testdata/HotelsScripts_Skytravelers.xlsx
+++ b/src/test/resources/testdata/HotelsScripts_Skytravelers.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AutomationScripts\Auto\src\test\resources\testdata\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AutomationScripts\TripGain_TestCases\src\test\resources\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9B204E9-B5B8-4465-95AA-01CB22B3ADB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25B77911-4EEB-4717-9FC8-D676A5261E04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="2" activeTab="6" xr2:uid="{512D99D7-B637-4054-871A-E0DB86511A8A}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="4" activeTab="6" xr2:uid="{512D99D7-B637-4054-871A-E0DB86511A8A}"/>
   </bookViews>
   <sheets>
     <sheet name="TCHO_1" sheetId="2" r:id="rId1"/>
@@ -18,16 +18,19 @@
     <sheet name="TCHO_3" sheetId="4" r:id="rId3"/>
     <sheet name="TCHO_4" sheetId="5" r:id="rId4"/>
     <sheet name="TCND_1" sheetId="6" r:id="rId5"/>
-    <sheet name="TCNDNEW_2" sheetId="15" r:id="rId6"/>
-    <sheet name="TCNDNEW_3" sheetId="16" r:id="rId7"/>
-    <sheet name="TCNDBU_1" sheetId="7" r:id="rId8"/>
-    <sheet name="TCNDBUNEW_2" sheetId="12" r:id="rId9"/>
-    <sheet name="exampletest" sheetId="11" r:id="rId10"/>
-    <sheet name="TCNDTR_1" sheetId="8" r:id="rId11"/>
-    <sheet name="TCNDTR_2" sheetId="9" r:id="rId12"/>
-    <sheet name="TCNDTR_3" sheetId="10" r:id="rId13"/>
-    <sheet name="TCNDBUNEW_3" sheetId="13" r:id="rId14"/>
-    <sheet name="TCNDBUNEW_4" sheetId="14" r:id="rId15"/>
+    <sheet name="TCND_2" sheetId="17" r:id="rId6"/>
+    <sheet name="TCNDFL_3" sheetId="18" r:id="rId7"/>
+    <sheet name="TCNDFL_4" sheetId="19" r:id="rId8"/>
+    <sheet name="TCNDNEW_2" sheetId="15" r:id="rId9"/>
+    <sheet name="TCNDNEW_3" sheetId="16" r:id="rId10"/>
+    <sheet name="TCNDBU_1" sheetId="7" r:id="rId11"/>
+    <sheet name="TCNDBUNEW_2" sheetId="12" r:id="rId12"/>
+    <sheet name="exampletest" sheetId="11" r:id="rId13"/>
+    <sheet name="TCNDTR_1" sheetId="8" r:id="rId14"/>
+    <sheet name="TCNDTR_2" sheetId="9" r:id="rId15"/>
+    <sheet name="TCNDTR_3" sheetId="10" r:id="rId16"/>
+    <sheet name="TCNDBUNEW_3" sheetId="13" r:id="rId17"/>
+    <sheet name="TCNDBUNEW_4" sheetId="14" r:id="rId18"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -50,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1864" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2042" uniqueCount="250">
   <si>
     <t>TestRun</t>
   </si>
@@ -749,13 +752,64 @@
   </si>
   <si>
     <t>https://weatherstack.com/</t>
+  </si>
+  <si>
+    <t>Class</t>
+  </si>
+  <si>
+    <t>TripType</t>
+  </si>
+  <si>
+    <t>Adults</t>
+  </si>
+  <si>
+    <t>SelectFlightIndex</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>FareType</t>
+  </si>
+  <si>
+    <t>Reason</t>
+  </si>
+  <si>
+    <t>https://neo.tripgain.com/</t>
+  </si>
+  <si>
+    <t>BLR</t>
+  </si>
+  <si>
+    <t>HYD</t>
+  </si>
+  <si>
+    <t>Economy</t>
+  </si>
+  <si>
+    <t>Oneway</t>
+  </si>
+  <si>
+    <t>Mr</t>
+  </si>
+  <si>
+    <t>Flexi</t>
+  </si>
+  <si>
+    <t>Better Flight Time</t>
+  </si>
+  <si>
+    <t>Round Trip</t>
+  </si>
+  <si>
+    <t>DXB</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -821,6 +875,19 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="9.8000000000000007"/>
+      <name val="Aptos Display"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Aptos Display"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -843,7 +910,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
@@ -863,6 +930,14 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2052,6 +2127,1151 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DB3B9C7-1D29-41A4-A6B6-F0B4AE1BA7DB}">
+  <dimension ref="A1:O2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="F1" t="s">
+        <v>205</v>
+      </c>
+      <c r="G1" t="s">
+        <v>206</v>
+      </c>
+      <c r="H1" t="s">
+        <v>208</v>
+      </c>
+      <c r="I1" t="s">
+        <v>209</v>
+      </c>
+      <c r="J1" t="s">
+        <v>211</v>
+      </c>
+      <c r="K1" t="s">
+        <v>213</v>
+      </c>
+      <c r="L1" t="s">
+        <v>215</v>
+      </c>
+      <c r="M1" t="s">
+        <v>216</v>
+      </c>
+      <c r="N1" t="s">
+        <v>217</v>
+      </c>
+      <c r="O1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="58" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2" t="s">
+        <v>207</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="K2" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="L2" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="M2" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="N2" s="10" t="s">
+        <v>214</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="M2" r:id="rId1" xr:uid="{A7158982-B3E9-4C29-A775-F8E84CFD6D5D}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D32C639-9751-46C8-AB5C-5BEC34FB1F52}">
+  <dimension ref="A1:O21"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="38.81640625" customWidth="1"/>
+    <col min="2" max="2" width="34.08984375" customWidth="1"/>
+    <col min="3" max="3" width="18.453125" customWidth="1"/>
+    <col min="4" max="4" width="13.81640625" customWidth="1"/>
+    <col min="5" max="5" width="15.54296875" customWidth="1"/>
+    <col min="6" max="6" width="19.90625" customWidth="1"/>
+    <col min="7" max="8" width="15.54296875" customWidth="1"/>
+    <col min="9" max="9" width="27.36328125" customWidth="1"/>
+    <col min="10" max="11" width="14.7265625" customWidth="1"/>
+    <col min="12" max="13" width="33.08984375" customWidth="1"/>
+    <col min="14" max="14" width="17.08984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="F1" t="s">
+        <v>205</v>
+      </c>
+      <c r="G1" t="s">
+        <v>206</v>
+      </c>
+      <c r="H1" t="s">
+        <v>208</v>
+      </c>
+      <c r="I1" t="s">
+        <v>209</v>
+      </c>
+      <c r="J1" t="s">
+        <v>211</v>
+      </c>
+      <c r="K1" t="s">
+        <v>213</v>
+      </c>
+      <c r="L1" t="s">
+        <v>215</v>
+      </c>
+      <c r="M1" t="s">
+        <v>216</v>
+      </c>
+      <c r="N1" t="s">
+        <v>217</v>
+      </c>
+      <c r="O1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="E2" t="s">
+        <v>140</v>
+      </c>
+      <c r="F2" t="s">
+        <v>207</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="K2" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="L2" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="M2" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="N2" s="10" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E3" t="s">
+        <v>141</v>
+      </c>
+      <c r="F3" t="s">
+        <v>207</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="K3" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="M3" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="N3" s="10" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" t="s">
+        <v>126</v>
+      </c>
+      <c r="F4" t="s">
+        <v>207</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="K4" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="M4" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="N4" s="10" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E5" t="s">
+        <v>142</v>
+      </c>
+      <c r="F5" t="s">
+        <v>207</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="K5" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="M5" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="N5" s="10" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A6" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="F6" t="s">
+        <v>207</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="K6" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="L6" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="M6" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="N6" s="10" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="F7" t="s">
+        <v>207</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="K7" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="M7" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="N7" s="10" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A8" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E8" t="s">
+        <v>146</v>
+      </c>
+      <c r="F8" t="s">
+        <v>207</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="K8" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="L8" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="M8" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="N8" s="10" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A9" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="E9" t="s">
+        <v>148</v>
+      </c>
+      <c r="F9" t="s">
+        <v>207</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="K9" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="M9" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="N9" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="O9" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A10" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="E10" t="s">
+        <v>150</v>
+      </c>
+      <c r="F10" t="s">
+        <v>207</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="K10" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="L10" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="M10" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="N10" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="O10" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A11" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="E11" t="s">
+        <v>152</v>
+      </c>
+      <c r="F11" t="s">
+        <v>207</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="J11" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="K11" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="M11" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="N11" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="O11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A12" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E12" t="s">
+        <v>153</v>
+      </c>
+      <c r="F12" t="s">
+        <v>207</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="K12" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="M12" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="N12" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="O12" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A13" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E13" t="s">
+        <v>155</v>
+      </c>
+      <c r="F13" t="s">
+        <v>207</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="J13" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="K13" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="M13" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="N13" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="O13" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A14" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E14" t="s">
+        <v>157</v>
+      </c>
+      <c r="F14" t="s">
+        <v>207</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="J14" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="K14" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="L14" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="M14" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="N14" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="O14" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A15" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E15" t="s">
+        <v>159</v>
+      </c>
+      <c r="F15" t="s">
+        <v>207</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="J15" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="K15" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="L15" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="M15" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="N15" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="O15" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A16" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E16" t="s">
+        <v>160</v>
+      </c>
+      <c r="F16" t="s">
+        <v>207</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="J16" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="K16" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="L16" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="M16" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="N16" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="O16" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A17" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E17" t="s">
+        <v>162</v>
+      </c>
+      <c r="F17" t="s">
+        <v>207</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="J17" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="K17" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="L17" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="M17" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="N17" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="O17" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A18" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E18" t="s">
+        <v>156</v>
+      </c>
+      <c r="F18" t="s">
+        <v>207</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I18" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="J18" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="K18" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="L18" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="M18" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="N18" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="O18" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A19" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="E19" t="s">
+        <v>164</v>
+      </c>
+      <c r="F19" t="s">
+        <v>207</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I19" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="J19" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="K19" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="L19" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="M19" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="N19" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="O19" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A20" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E20" t="s">
+        <v>165</v>
+      </c>
+      <c r="F20" t="s">
+        <v>207</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I20" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="J20" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="K20" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="L20" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="M20" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="N20" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="O20" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A21" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="E21" t="s">
+        <v>167</v>
+      </c>
+      <c r="F21" t="s">
+        <v>207</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I21" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="J21" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="K21" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="L21" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="M21" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="N21" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="O21" t="s">
+        <v>120</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="M2" r:id="rId1" xr:uid="{9BEAB127-63D2-4FEF-A0FF-397BA8766D43}"/>
+    <hyperlink ref="M3:M20" r:id="rId2" display="testfinanceadmin98@tripgain.com" xr:uid="{68F8BB36-A177-4C38-B645-680DBC174201}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0141A322-4E7A-40FA-A28F-5FC73A1002A7}">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="F1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="E2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0015B3CF-9070-4AB0-A8B1-769A8784C11C}">
   <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -2125,7 +3345,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B67CCBB0-59C0-48CB-A87A-0B0C4F1FD065}">
   <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -2183,7 +3403,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B601A09D-93F0-4AB8-824B-DB778A997F8A}">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -2227,7 +3447,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3D33E6F-A6B1-4616-954D-27E1D6F16508}">
   <dimension ref="A1:J16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -2710,7 +3930,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D2A165B-C0AE-450E-8DD8-0A7073A78BBC}">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -2757,7 +3977,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0097D35B-A3B5-43FF-807C-CC910EC043F4}">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -5449,7 +6669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="29" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>202</v>
       </c>
@@ -5500,9 +6720,7 @@
       <c r="B3" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>204</v>
-      </c>
+      <c r="C3" s="2"/>
       <c r="D3" s="1" t="s">
         <v>39</v>
       </c>
@@ -5535,6 +6753,9 @@
       </c>
       <c r="N3" s="10" t="s">
         <v>214</v>
+      </c>
+      <c r="O3" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.35">
@@ -5580,6 +6801,9 @@
       <c r="N4" s="10" t="s">
         <v>214</v>
       </c>
+      <c r="O4" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
@@ -5624,6 +6848,9 @@
       <c r="N5" s="10" t="s">
         <v>214</v>
       </c>
+      <c r="O5" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
@@ -5668,6 +6895,9 @@
       <c r="N6" s="10" t="s">
         <v>214</v>
       </c>
+      <c r="O6" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
@@ -5712,6 +6942,9 @@
       <c r="N7" s="10" t="s">
         <v>214</v>
       </c>
+      <c r="O7" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
@@ -5756,6 +6989,9 @@
       <c r="N8" s="10" t="s">
         <v>214</v>
       </c>
+      <c r="O8" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
@@ -5800,6 +7036,9 @@
       <c r="N9" s="10" t="s">
         <v>214</v>
       </c>
+      <c r="O9" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
@@ -5844,6 +7083,9 @@
       <c r="N10" s="10" t="s">
         <v>214</v>
       </c>
+      <c r="O10" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
@@ -5888,6 +7130,9 @@
       <c r="N11" s="10" t="s">
         <v>214</v>
       </c>
+      <c r="O11" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
@@ -5932,6 +7177,9 @@
       <c r="N12" s="10" t="s">
         <v>214</v>
       </c>
+      <c r="O12" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
@@ -5976,6 +7224,9 @@
       <c r="N13" s="10" t="s">
         <v>214</v>
       </c>
+      <c r="O13" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
@@ -6020,6 +7271,9 @@
       <c r="N14" s="10" t="s">
         <v>214</v>
       </c>
+      <c r="O14" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
@@ -6064,6 +7318,9 @@
       <c r="N15" s="10" t="s">
         <v>214</v>
       </c>
+      <c r="O15" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
@@ -6108,8 +7365,11 @@
       <c r="N16" s="10" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O16" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>202</v>
       </c>
@@ -6152,8 +7412,11 @@
       <c r="N17" s="10" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O17" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>202</v>
       </c>
@@ -6196,8 +7459,11 @@
       <c r="N18" s="10" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O18" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>202</v>
       </c>
@@ -6240,8 +7506,11 @@
       <c r="N19" s="10" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O19" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>202</v>
       </c>
@@ -6284,8 +7553,11 @@
       <c r="N20" s="10" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O20" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>202</v>
       </c>
@@ -6328,8 +7600,11 @@
       <c r="N21" s="10" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O21" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>202</v>
       </c>
@@ -6372,8 +7647,11 @@
       <c r="N22" s="10" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O22" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>202</v>
       </c>
@@ -6416,8 +7694,11 @@
       <c r="N23" s="10" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O23" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>202</v>
       </c>
@@ -6460,8 +7741,11 @@
       <c r="N24" s="10" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O24" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>202</v>
       </c>
@@ -6504,8 +7788,11 @@
       <c r="N25" s="10" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O25" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>202</v>
       </c>
@@ -6548,8 +7835,11 @@
       <c r="N26" s="10" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O26" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>202</v>
       </c>
@@ -6592,8 +7882,11 @@
       <c r="N27" s="10" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O27" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>202</v>
       </c>
@@ -6636,8 +7929,11 @@
       <c r="N28" s="10" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O28" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>202</v>
       </c>
@@ -6680,8 +7976,11 @@
       <c r="N29" s="10" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O29" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>202</v>
       </c>
@@ -6724,8 +8023,11 @@
       <c r="N30" s="10" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O30" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
         <v>202</v>
       </c>
@@ -6768,8 +8070,11 @@
       <c r="N31" s="10" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O31" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
         <v>202</v>
       </c>
@@ -6812,8 +8117,11 @@
       <c r="N32" s="10" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O32" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
         <v>202</v>
       </c>
@@ -6856,8 +8164,11 @@
       <c r="N33" s="10" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O33" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
         <v>202</v>
       </c>
@@ -6900,8 +8211,11 @@
       <c r="N34" s="10" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O34" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
         <v>202</v>
       </c>
@@ -6944,8 +8258,11 @@
       <c r="N35" s="10" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O35" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
         <v>202</v>
       </c>
@@ -6988,8 +8305,11 @@
       <c r="N36" s="10" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O36" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
         <v>202</v>
       </c>
@@ -7032,8 +8352,11 @@
       <c r="N37" s="10" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O37" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
         <v>202</v>
       </c>
@@ -7076,8 +8399,11 @@
       <c r="N38" s="10" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O38" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
         <v>202</v>
       </c>
@@ -7120,8 +8446,11 @@
       <c r="N39" s="10" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O39" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
         <v>202</v>
       </c>
@@ -7164,8 +8493,11 @@
       <c r="N40" s="10" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O40" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
         <v>202</v>
       </c>
@@ -7208,8 +8540,11 @@
       <c r="N41" s="10" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O41" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
         <v>202</v>
       </c>
@@ -7252,8 +8587,11 @@
       <c r="N42" s="10" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O42" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
         <v>202</v>
       </c>
@@ -7296,8 +8634,11 @@
       <c r="N43" s="10" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O43" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
         <v>202</v>
       </c>
@@ -7340,8 +8681,11 @@
       <c r="N44" s="10" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O44" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
         <v>202</v>
       </c>
@@ -7384,8 +8728,11 @@
       <c r="N45" s="10" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O45" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
         <v>202</v>
       </c>
@@ -7428,8 +8775,11 @@
       <c r="N46" s="10" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O46" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
         <v>202</v>
       </c>
@@ -7472,8 +8822,11 @@
       <c r="N47" s="10" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O47" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
         <v>202</v>
       </c>
@@ -7516,8 +8869,11 @@
       <c r="N48" s="10" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O48" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
         <v>202</v>
       </c>
@@ -7560,8 +8916,11 @@
       <c r="N49" s="10" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O49" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
         <v>202</v>
       </c>
@@ -7604,8 +8963,11 @@
       <c r="N50" s="10" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O50" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
         <v>202</v>
       </c>
@@ -7647,6 +9009,9 @@
       </c>
       <c r="N51" s="10" t="s">
         <v>214</v>
+      </c>
+      <c r="O51" t="s">
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -7654,12 +9019,511 @@
   <hyperlinks>
     <hyperlink ref="M2" r:id="rId1" xr:uid="{CCA707E1-4567-4C38-B7DE-0422E4B7EFEF}"/>
     <hyperlink ref="M3:M51" r:id="rId2" display="testfinanceadmin98@tripgain.com" xr:uid="{55372BF5-A41F-4C9E-9C8A-42BFEAD79DED}"/>
+    <hyperlink ref="B2" r:id="rId3" xr:uid="{793A0C57-0A27-44C4-84C9-EBFC97D3785B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D384A220-749F-4167-AC55-B1AF55FE5E04}">
+  <dimension ref="A1:O6"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="5" max="5" width="15.54296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="F1" t="s">
+        <v>205</v>
+      </c>
+      <c r="G1" t="s">
+        <v>206</v>
+      </c>
+      <c r="H1" t="s">
+        <v>208</v>
+      </c>
+      <c r="I1" t="s">
+        <v>209</v>
+      </c>
+      <c r="J1" t="s">
+        <v>211</v>
+      </c>
+      <c r="K1" t="s">
+        <v>213</v>
+      </c>
+      <c r="L1" t="s">
+        <v>215</v>
+      </c>
+      <c r="M1" t="s">
+        <v>216</v>
+      </c>
+      <c r="N1" t="s">
+        <v>217</v>
+      </c>
+      <c r="O1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="58" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2" t="s">
+        <v>207</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="K2" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="L2" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="M2" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="N2" s="10" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="58" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E3">
+        <v>3</v>
+      </c>
+      <c r="F3" t="s">
+        <v>207</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="K3" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="M3" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="N3" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="O3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="58" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E4">
+        <v>3</v>
+      </c>
+      <c r="F4" t="s">
+        <v>207</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="K4" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="M4" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="N4" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="O4" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="58" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5" t="s">
+        <v>207</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="K5" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="M5" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="N5" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="O5" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="58" x14ac:dyDescent="0.35">
+      <c r="A6" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6" t="s">
+        <v>207</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="K6" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="L6" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="M6" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="N6" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="O6" t="s">
+        <v>120</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="M2" r:id="rId1" xr:uid="{62555C73-CF83-4045-B312-36E8EB8B2895}"/>
+    <hyperlink ref="M3" r:id="rId2" xr:uid="{D90F5E9B-CF9E-44EF-9F4C-2219A3403C67}"/>
+    <hyperlink ref="M4" r:id="rId3" xr:uid="{1B2C186A-5933-4CBD-BB1A-A39E2DDA92F5}"/>
+    <hyperlink ref="M5" r:id="rId4" xr:uid="{6B343328-ADEE-4D68-BCE7-10C2CF818BE8}"/>
+    <hyperlink ref="M6" r:id="rId5" xr:uid="{DBE12985-1328-44B9-BB95-242CAE090E8D}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1F3EEA5-DCC3-4074-B026-57499537C17E}">
+  <dimension ref="A1:M2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="21.36328125" customWidth="1"/>
+    <col min="2" max="2" width="25.54296875" customWidth="1"/>
+    <col min="3" max="3" width="21.81640625" customWidth="1"/>
+    <col min="9" max="9" width="22.90625" customWidth="1"/>
+    <col min="12" max="12" width="20.1796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" t="s">
+        <v>138</v>
+      </c>
+      <c r="F1" t="s">
+        <v>233</v>
+      </c>
+      <c r="G1" t="s">
+        <v>234</v>
+      </c>
+      <c r="H1" t="s">
+        <v>235</v>
+      </c>
+      <c r="I1" t="s">
+        <v>236</v>
+      </c>
+      <c r="J1" s="12" t="s">
+        <v>237</v>
+      </c>
+      <c r="K1" t="s">
+        <v>238</v>
+      </c>
+      <c r="L1" t="s">
+        <v>239</v>
+      </c>
+      <c r="M1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A2" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="F2" t="s">
+        <v>243</v>
+      </c>
+      <c r="G2" s="14" t="s">
+        <v>244</v>
+      </c>
+      <c r="H2" s="15">
+        <v>1</v>
+      </c>
+      <c r="I2" s="15">
+        <v>2</v>
+      </c>
+      <c r="J2" s="15" t="s">
+        <v>245</v>
+      </c>
+      <c r="K2" s="15" t="s">
+        <v>246</v>
+      </c>
+      <c r="L2" s="15" t="s">
+        <v>247</v>
+      </c>
+      <c r="M2" s="15"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{72C8C5FC-36D8-4490-A4D0-8C9B284C3C12}"/>
+    <hyperlink ref="A2" r:id="rId2" tooltip="https://neo.tripgain.com/" xr:uid="{BEC5EDF2-93B1-4C7E-AEE6-859FF732A550}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28E34583-02BB-49FD-9732-540EBD790FDF}">
+  <dimension ref="A1:M2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="6" max="6" width="15.81640625" customWidth="1"/>
+    <col min="11" max="11" width="17.90625" customWidth="1"/>
+    <col min="12" max="12" width="25.36328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E1" t="s">
+        <v>233</v>
+      </c>
+      <c r="F1" t="s">
+        <v>234</v>
+      </c>
+      <c r="G1" t="s">
+        <v>235</v>
+      </c>
+      <c r="H1" t="s">
+        <v>236</v>
+      </c>
+      <c r="I1" s="12" t="s">
+        <v>237</v>
+      </c>
+      <c r="J1" t="s">
+        <v>238</v>
+      </c>
+      <c r="K1" t="s">
+        <v>239</v>
+      </c>
+      <c r="L1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A2" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E2" t="s">
+        <v>243</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="G2" s="15">
+        <v>1</v>
+      </c>
+      <c r="H2" s="15">
+        <v>2</v>
+      </c>
+      <c r="I2" s="15" t="s">
+        <v>245</v>
+      </c>
+      <c r="J2" s="15" t="s">
+        <v>246</v>
+      </c>
+      <c r="K2" s="15" t="s">
+        <v>247</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>240</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1" xr:uid="{39C31F05-F2F5-4281-A609-3C22A9BB2384}"/>
+    <hyperlink ref="L2" r:id="rId2" tooltip="https://neo.tripgain.com/" xr:uid="{C4305805-391B-486A-B640-6826D82A959D}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1594D560-AC0A-434C-82B6-21B802CD2CA5}">
   <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -7761,1149 +9625,4 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DB3B9C7-1D29-41A4-A6B6-F0B4AE1BA7DB}">
-  <dimension ref="A1:O2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="F1" t="s">
-        <v>205</v>
-      </c>
-      <c r="G1" t="s">
-        <v>206</v>
-      </c>
-      <c r="H1" t="s">
-        <v>208</v>
-      </c>
-      <c r="I1" t="s">
-        <v>209</v>
-      </c>
-      <c r="J1" t="s">
-        <v>211</v>
-      </c>
-      <c r="K1" t="s">
-        <v>213</v>
-      </c>
-      <c r="L1" t="s">
-        <v>215</v>
-      </c>
-      <c r="M1" t="s">
-        <v>216</v>
-      </c>
-      <c r="N1" t="s">
-        <v>217</v>
-      </c>
-      <c r="O1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" ht="58" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2" t="s">
-        <v>207</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="J2" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="K2" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L2" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M2" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N2" s="10" t="s">
-        <v>214</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="M2" r:id="rId1" xr:uid="{A7158982-B3E9-4C29-A775-F8E84CFD6D5D}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D32C639-9751-46C8-AB5C-5BEC34FB1F52}">
-  <dimension ref="A1:O21"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="38.81640625" customWidth="1"/>
-    <col min="2" max="2" width="34.08984375" customWidth="1"/>
-    <col min="3" max="3" width="18.453125" customWidth="1"/>
-    <col min="4" max="4" width="13.81640625" customWidth="1"/>
-    <col min="5" max="5" width="15.54296875" customWidth="1"/>
-    <col min="6" max="6" width="19.90625" customWidth="1"/>
-    <col min="7" max="8" width="15.54296875" customWidth="1"/>
-    <col min="9" max="9" width="27.36328125" customWidth="1"/>
-    <col min="10" max="11" width="14.7265625" customWidth="1"/>
-    <col min="12" max="13" width="33.08984375" customWidth="1"/>
-    <col min="14" max="14" width="17.08984375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="F1" t="s">
-        <v>205</v>
-      </c>
-      <c r="G1" t="s">
-        <v>206</v>
-      </c>
-      <c r="H1" t="s">
-        <v>208</v>
-      </c>
-      <c r="I1" t="s">
-        <v>209</v>
-      </c>
-      <c r="J1" t="s">
-        <v>211</v>
-      </c>
-      <c r="K1" t="s">
-        <v>213</v>
-      </c>
-      <c r="L1" t="s">
-        <v>215</v>
-      </c>
-      <c r="M1" t="s">
-        <v>216</v>
-      </c>
-      <c r="N1" t="s">
-        <v>217</v>
-      </c>
-      <c r="O1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="E2" t="s">
-        <v>140</v>
-      </c>
-      <c r="F2" t="s">
-        <v>207</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="J2" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="K2" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L2" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M2" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N2" s="10" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E3" t="s">
-        <v>141</v>
-      </c>
-      <c r="F3" t="s">
-        <v>207</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="K3" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L3" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M3" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N3" s="10" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E4" t="s">
-        <v>126</v>
-      </c>
-      <c r="F4" t="s">
-        <v>207</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="J4" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="K4" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L4" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M4" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N4" s="10" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A5" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E5" t="s">
-        <v>142</v>
-      </c>
-      <c r="F5" t="s">
-        <v>207</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="I5" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="J5" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="K5" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L5" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M5" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N5" s="10" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A6" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="F6" t="s">
-        <v>207</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="I6" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="J6" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="K6" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L6" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M6" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N6" s="10" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A7" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="F7" t="s">
-        <v>207</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="I7" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="J7" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="K7" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L7" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M7" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N7" s="10" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A8" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E8" t="s">
-        <v>146</v>
-      </c>
-      <c r="F8" t="s">
-        <v>207</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="I8" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="J8" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="K8" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L8" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M8" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N8" s="10" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A9" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="E9" t="s">
-        <v>148</v>
-      </c>
-      <c r="F9" t="s">
-        <v>207</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="J9" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="K9" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L9" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M9" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N9" s="10" t="s">
-        <v>214</v>
-      </c>
-      <c r="O9" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A10" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="E10" t="s">
-        <v>150</v>
-      </c>
-      <c r="F10" t="s">
-        <v>207</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="J10" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="K10" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L10" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M10" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N10" s="10" t="s">
-        <v>214</v>
-      </c>
-      <c r="O10" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A11" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="E11" t="s">
-        <v>152</v>
-      </c>
-      <c r="F11" t="s">
-        <v>207</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="I11" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="J11" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="K11" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L11" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M11" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N11" s="10" t="s">
-        <v>214</v>
-      </c>
-      <c r="O11" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A12" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="E12" t="s">
-        <v>153</v>
-      </c>
-      <c r="F12" t="s">
-        <v>207</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="I12" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="J12" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="K12" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L12" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M12" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N12" s="10" t="s">
-        <v>214</v>
-      </c>
-      <c r="O12" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A13" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="E13" t="s">
-        <v>155</v>
-      </c>
-      <c r="F13" t="s">
-        <v>207</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="I13" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="J13" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="K13" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L13" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M13" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N13" s="10" t="s">
-        <v>214</v>
-      </c>
-      <c r="O13" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A14" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="E14" t="s">
-        <v>157</v>
-      </c>
-      <c r="F14" t="s">
-        <v>207</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="H14" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="I14" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="J14" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="K14" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L14" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M14" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N14" s="10" t="s">
-        <v>214</v>
-      </c>
-      <c r="O14" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A15" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="E15" t="s">
-        <v>159</v>
-      </c>
-      <c r="F15" t="s">
-        <v>207</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="I15" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="J15" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="K15" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L15" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M15" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N15" s="10" t="s">
-        <v>214</v>
-      </c>
-      <c r="O15" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A16" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="E16" t="s">
-        <v>160</v>
-      </c>
-      <c r="F16" t="s">
-        <v>207</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="H16" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="I16" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="J16" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="K16" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L16" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M16" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N16" s="10" t="s">
-        <v>214</v>
-      </c>
-      <c r="O16" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A17" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="E17" t="s">
-        <v>162</v>
-      </c>
-      <c r="F17" t="s">
-        <v>207</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="H17" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="I17" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="J17" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="K17" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L17" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M17" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N17" s="10" t="s">
-        <v>214</v>
-      </c>
-      <c r="O17" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A18" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E18" t="s">
-        <v>156</v>
-      </c>
-      <c r="F18" t="s">
-        <v>207</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="H18" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="I18" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="J18" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="K18" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L18" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M18" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N18" s="10" t="s">
-        <v>214</v>
-      </c>
-      <c r="O18" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A19" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="E19" t="s">
-        <v>164</v>
-      </c>
-      <c r="F19" t="s">
-        <v>207</v>
-      </c>
-      <c r="G19" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="H19" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="I19" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="J19" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="K19" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L19" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M19" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N19" s="10" t="s">
-        <v>214</v>
-      </c>
-      <c r="O19" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A20" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E20" t="s">
-        <v>165</v>
-      </c>
-      <c r="F20" t="s">
-        <v>207</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="H20" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="I20" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="J20" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="K20" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L20" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M20" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N20" s="10" t="s">
-        <v>214</v>
-      </c>
-      <c r="O20" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A21" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="E21" t="s">
-        <v>167</v>
-      </c>
-      <c r="F21" t="s">
-        <v>207</v>
-      </c>
-      <c r="G21" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="H21" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="I21" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="J21" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="K21" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L21" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M21" s="8" t="s">
-        <v>231</v>
-      </c>
-      <c r="N21" s="10" t="s">
-        <v>214</v>
-      </c>
-      <c r="O21" t="s">
-        <v>120</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="M2" r:id="rId1" xr:uid="{9BEAB127-63D2-4FEF-A0FF-397BA8766D43}"/>
-    <hyperlink ref="M3:M20" r:id="rId2" display="testfinanceadmin98@tripgain.com" xr:uid="{68F8BB36-A177-4C38-B645-680DBC174201}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0141A322-4E7A-40FA-A28F-5FC73A1002A7}">
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="F1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="E2" t="s">
-        <v>140</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/src/test/resources/testdata/HotelsScripts_Skytravelers.xlsx
+++ b/src/test/resources/testdata/HotelsScripts_Skytravelers.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AutomationScripts\TripGain_TestCases\src\test\resources\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25B77911-4EEB-4717-9FC8-D676A5261E04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{013B0A78-CF6B-4345-8A79-B1C4E3B87A0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="4" activeTab="6" xr2:uid="{512D99D7-B637-4054-871A-E0DB86511A8A}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="11" activeTab="14" xr2:uid="{512D99D7-B637-4054-871A-E0DB86511A8A}"/>
   </bookViews>
   <sheets>
     <sheet name="TCHO_1" sheetId="2" r:id="rId1"/>
@@ -19,18 +19,19 @@
     <sheet name="TCHO_4" sheetId="5" r:id="rId4"/>
     <sheet name="TCND_1" sheetId="6" r:id="rId5"/>
     <sheet name="TCND_2" sheetId="17" r:id="rId6"/>
-    <sheet name="TCNDFL_3" sheetId="18" r:id="rId7"/>
-    <sheet name="TCNDFL_4" sheetId="19" r:id="rId8"/>
-    <sheet name="TCNDNEW_2" sheetId="15" r:id="rId9"/>
-    <sheet name="TCNDNEW_3" sheetId="16" r:id="rId10"/>
-    <sheet name="TCNDBU_1" sheetId="7" r:id="rId11"/>
-    <sheet name="TCNDBUNEW_2" sheetId="12" r:id="rId12"/>
-    <sheet name="exampletest" sheetId="11" r:id="rId13"/>
-    <sheet name="TCNDTR_1" sheetId="8" r:id="rId14"/>
-    <sheet name="TCNDTR_2" sheetId="9" r:id="rId15"/>
-    <sheet name="TCNDTR_3" sheetId="10" r:id="rId16"/>
-    <sheet name="TCNDBUNEW_3" sheetId="13" r:id="rId17"/>
-    <sheet name="TCNDBUNEW_4" sheetId="14" r:id="rId18"/>
+    <sheet name="TCND_3" sheetId="20" r:id="rId7"/>
+    <sheet name="TCNDFL_3" sheetId="18" r:id="rId8"/>
+    <sheet name="TCNDFL_4" sheetId="19" r:id="rId9"/>
+    <sheet name="TCNDNEW_2" sheetId="15" r:id="rId10"/>
+    <sheet name="TCNDNEW_3" sheetId="16" r:id="rId11"/>
+    <sheet name="TCNDBU_1" sheetId="7" r:id="rId12"/>
+    <sheet name="TCNDBUNEW_2" sheetId="12" r:id="rId13"/>
+    <sheet name="exampletest" sheetId="11" r:id="rId14"/>
+    <sheet name="TCNDTR_1" sheetId="8" r:id="rId15"/>
+    <sheet name="TCNDTR_2" sheetId="9" r:id="rId16"/>
+    <sheet name="TCNDTR_3" sheetId="10" r:id="rId17"/>
+    <sheet name="TCNDBUNEW_3" sheetId="13" r:id="rId18"/>
+    <sheet name="TCNDBUNEW_4" sheetId="14" r:id="rId19"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -53,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2042" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2077" uniqueCount="256">
   <si>
     <t>TestRun</t>
   </si>
@@ -418,15 +419,9 @@
     <t>SKIP</t>
   </si>
   <si>
-    <t>testtraveller907@gmail.com</t>
-  </si>
-  <si>
     <t>https://tgdev.tripgain.com/</t>
   </si>
   <si>
-    <t>Doordie@100</t>
-  </si>
-  <si>
     <t>kengeri</t>
   </si>
   <si>
@@ -802,7 +797,31 @@
     <t>Round Trip</t>
   </si>
   <si>
-    <t>DXB</t>
+    <t>s</t>
+  </si>
+  <si>
+    <t>BZV</t>
+  </si>
+  <si>
+    <t>FIH</t>
+  </si>
+  <si>
+    <t>https://appv2.tripgain.com/login</t>
+  </si>
+  <si>
+    <t>admin@testqa.com</t>
+  </si>
+  <si>
+    <t>Qa@TG234!!</t>
+  </si>
+  <si>
+    <t>testfinance98@tripgain.com</t>
+  </si>
+  <si>
+    <t>ApproverSearchValue</t>
+  </si>
+  <si>
+    <t>ApproverSearchValue2</t>
   </si>
 </sst>
 </file>
@@ -864,12 +883,6 @@
       <family val="3"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF667085"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color rgb="FF667085"/>
       <name val="Arial"/>
@@ -887,6 +900,12 @@
       <name val="Aptos Display"/>
       <family val="2"/>
       <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -924,21 +943,19 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2127,6 +2144,110 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1594D560-AC0A-434C-82B6-21B802CD2CA5}">
+  <dimension ref="A1:O2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="F1" t="s">
+        <v>203</v>
+      </c>
+      <c r="G1" t="s">
+        <v>204</v>
+      </c>
+      <c r="H1" t="s">
+        <v>206</v>
+      </c>
+      <c r="I1" t="s">
+        <v>207</v>
+      </c>
+      <c r="J1" t="s">
+        <v>209</v>
+      </c>
+      <c r="K1" t="s">
+        <v>211</v>
+      </c>
+      <c r="L1" t="s">
+        <v>213</v>
+      </c>
+      <c r="M1" t="s">
+        <v>214</v>
+      </c>
+      <c r="N1" t="s">
+        <v>215</v>
+      </c>
+      <c r="O1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="58" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2" t="s">
+        <v>205</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="K2" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L2" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M2" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="N2" s="9" t="s">
+        <v>212</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="M2" r:id="rId1" xr:uid="{7F7B95CD-2341-4E68-B495-28B6BB9649F5}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DB3B9C7-1D29-41A4-A6B6-F0B4AE1BA7DB}">
   <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -2145,34 +2266,34 @@
         <v>1</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="G1" t="s">
+        <v>204</v>
+      </c>
+      <c r="H1" t="s">
         <v>206</v>
       </c>
-      <c r="H1" t="s">
-        <v>208</v>
-      </c>
       <c r="I1" t="s">
+        <v>207</v>
+      </c>
+      <c r="J1" t="s">
         <v>209</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>211</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>213</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
+        <v>214</v>
+      </c>
+      <c r="N1" t="s">
         <v>215</v>
-      </c>
-      <c r="M1" t="s">
-        <v>216</v>
-      </c>
-      <c r="N1" t="s">
-        <v>217</v>
       </c>
       <c r="O1" t="s">
         <v>0</v>
@@ -2180,13 +2301,13 @@
     </row>
     <row r="2" spans="1:15" ht="58" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>39</v>
@@ -2195,31 +2316,31 @@
         <v>2</v>
       </c>
       <c r="F2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H2" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="9" t="s">
+      <c r="I2" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J2" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="J2" s="9" t="s">
+      <c r="K2" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L2" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M2" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="N2" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="K2" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L2" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M2" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N2" s="10" t="s">
-        <v>214</v>
       </c>
     </row>
   </sheetData>
@@ -2230,7 +2351,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D32C639-9751-46C8-AB5C-5BEC34FB1F52}">
   <dimension ref="A1:O21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -2262,34 +2383,34 @@
         <v>1</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="G1" t="s">
+        <v>204</v>
+      </c>
+      <c r="H1" t="s">
         <v>206</v>
       </c>
-      <c r="H1" t="s">
-        <v>208</v>
-      </c>
       <c r="I1" t="s">
+        <v>254</v>
+      </c>
+      <c r="J1" t="s">
         <v>209</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>211</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>213</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
+        <v>255</v>
+      </c>
+      <c r="N1" t="s">
         <v>215</v>
-      </c>
-      <c r="M1" t="s">
-        <v>216</v>
-      </c>
-      <c r="N1" t="s">
-        <v>217</v>
       </c>
       <c r="O1" t="s">
         <v>0</v>
@@ -2297,354 +2418,372 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H2" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="9" t="s">
+      <c r="I2" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J2" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="J2" s="9" t="s">
+      <c r="K2" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L2" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M2" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="N2" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="K2" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L2" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M2" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N2" s="10" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F3" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="I3" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J3" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="K3" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M3" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="N3" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="K3" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L3" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M3" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N3" s="10" t="s">
-        <v>214</v>
+      <c r="O3" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>27</v>
       </c>
       <c r="E4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F4" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H4" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="I4" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J4" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="J4" s="9" t="s">
+      <c r="K4" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M4" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="N4" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="K4" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L4" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M4" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N4" s="10" t="s">
-        <v>214</v>
+      <c r="O4" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>49</v>
       </c>
       <c r="E5" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F5" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H5" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I5" s="9" t="s">
+      <c r="I5" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J5" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="J5" s="9" t="s">
+      <c r="K5" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M5" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="N5" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="K5" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L5" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M5" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N5" s="10" t="s">
-        <v>214</v>
+      <c r="O5" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F6" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H6" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I6" s="9" t="s">
+      <c r="I6" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J6" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="J6" s="9" t="s">
+      <c r="K6" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M6" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="N6" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="K6" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L6" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M6" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N6" s="10" t="s">
-        <v>214</v>
+      <c r="O6" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>42</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F7" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H7" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I7" s="9" t="s">
+      <c r="I7" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J7" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="J7" s="9" t="s">
+      <c r="K7" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M7" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="N7" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="K7" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L7" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M7" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N7" s="10" t="s">
-        <v>214</v>
+      <c r="O7" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>48</v>
       </c>
       <c r="E8" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F8" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H8" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I8" s="9" t="s">
+      <c r="I8" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J8" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="J8" s="9" t="s">
+      <c r="K8" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M8" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="N8" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="K8" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L8" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M8" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N8" s="10" t="s">
-        <v>214</v>
+      <c r="O8" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E9" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F9" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H9" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I9" s="9" t="s">
+      <c r="I9" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J9" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="J9" s="9" t="s">
+      <c r="K9" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M9" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="N9" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="K9" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L9" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M9" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N9" s="10" t="s">
-        <v>214</v>
       </c>
       <c r="O9" t="s">
         <v>120</v>
@@ -2652,46 +2791,46 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E10" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F10" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H10" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I10" s="9" t="s">
+      <c r="I10" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J10" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="J10" s="9" t="s">
+      <c r="K10" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M10" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="N10" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="K10" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L10" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M10" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N10" s="10" t="s">
-        <v>214</v>
       </c>
       <c r="O10" t="s">
         <v>120</v>
@@ -2699,46 +2838,46 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E11" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="F11" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H11" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I11" s="9" t="s">
+      <c r="I11" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J11" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="J11" s="9" t="s">
+      <c r="K11" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M11" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="N11" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="K11" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L11" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M11" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N11" s="10" t="s">
-        <v>214</v>
       </c>
       <c r="O11" t="s">
         <v>120</v>
@@ -2746,46 +2885,46 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>59</v>
       </c>
       <c r="E12" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F12" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H12" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I12" s="9" t="s">
+      <c r="I12" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J12" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="J12" s="9" t="s">
+      <c r="K12" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M12" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="N12" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="K12" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L12" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M12" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N12" s="10" t="s">
-        <v>214</v>
       </c>
       <c r="O12" t="s">
         <v>120</v>
@@ -2793,46 +2932,46 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E13" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F13" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H13" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I13" s="9" t="s">
+      <c r="I13" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J13" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="J13" s="9" t="s">
+      <c r="K13" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L13" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M13" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="N13" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="K13" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L13" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M13" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N13" s="10" t="s">
-        <v>214</v>
       </c>
       <c r="O13" t="s">
         <v>120</v>
@@ -2840,46 +2979,46 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E14" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="F14" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H14" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I14" s="9" t="s">
+      <c r="I14" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J14" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="J14" s="9" t="s">
+      <c r="K14" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M14" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="N14" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="K14" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L14" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M14" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N14" s="10" t="s">
-        <v>214</v>
       </c>
       <c r="O14" t="s">
         <v>120</v>
@@ -2887,46 +3026,46 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E15" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F15" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H15" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I15" s="9" t="s">
+      <c r="I15" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J15" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="J15" s="9" t="s">
+      <c r="K15" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M15" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="N15" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="K15" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L15" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M15" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N15" s="10" t="s">
-        <v>214</v>
       </c>
       <c r="O15" t="s">
         <v>120</v>
@@ -2934,46 +3073,46 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E16" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F16" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H16" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I16" s="9" t="s">
+      <c r="I16" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J16" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="J16" s="9" t="s">
+      <c r="K16" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M16" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="N16" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="K16" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L16" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M16" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N16" s="10" t="s">
-        <v>214</v>
       </c>
       <c r="O16" t="s">
         <v>120</v>
@@ -2981,46 +3120,46 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E17" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F17" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H17" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I17" s="9" t="s">
+      <c r="I17" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J17" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="J17" s="9" t="s">
+      <c r="K17" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M17" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="N17" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="K17" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L17" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M17" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N17" s="10" t="s">
-        <v>214</v>
       </c>
       <c r="O17" t="s">
         <v>120</v>
@@ -3028,46 +3167,46 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E18" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F18" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H18" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I18" s="9" t="s">
+      <c r="I18" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J18" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="J18" s="9" t="s">
+      <c r="K18" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M18" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="N18" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="K18" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L18" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M18" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N18" s="10" t="s">
-        <v>214</v>
       </c>
       <c r="O18" t="s">
         <v>120</v>
@@ -3075,46 +3214,46 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E19" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F19" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H19" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I19" s="9" t="s">
+      <c r="I19" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J19" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="J19" s="9" t="s">
+      <c r="K19" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M19" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="N19" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="K19" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L19" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M19" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N19" s="10" t="s">
-        <v>214</v>
       </c>
       <c r="O19" t="s">
         <v>120</v>
@@ -3122,46 +3261,46 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>49</v>
       </c>
       <c r="E20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F20" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H20" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I20" s="9" t="s">
+      <c r="I20" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J20" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="J20" s="9" t="s">
+      <c r="K20" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L20" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M20" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="N20" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="K20" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L20" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M20" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N20" s="10" t="s">
-        <v>214</v>
       </c>
       <c r="O20" t="s">
         <v>120</v>
@@ -3169,46 +3308,46 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E21" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F21" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H21" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I21" s="9" t="s">
+      <c r="I21" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J21" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="J21" s="9" t="s">
+      <c r="K21" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L21" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M21" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="N21" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="K21" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L21" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M21" s="8" t="s">
-        <v>231</v>
-      </c>
-      <c r="N21" s="10" t="s">
-        <v>214</v>
       </c>
       <c r="O21" t="s">
         <v>120</v>
@@ -3218,13 +3357,13 @@
   <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="M2" r:id="rId1" xr:uid="{9BEAB127-63D2-4FEF-A0FF-397BA8766D43}"/>
-    <hyperlink ref="M3:M20" r:id="rId2" display="testfinanceadmin98@tripgain.com" xr:uid="{68F8BB36-A177-4C38-B645-680DBC174201}"/>
+    <hyperlink ref="M3:M21" r:id="rId2" display="testfinance98@tripgain.com" xr:uid="{4B1CAC94-FE13-46D0-9AFA-9C0A24D8B7D2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0141A322-4E7A-40FA-A28F-5FC73A1002A7}">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -3243,7 +3382,7 @@
         <v>1</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F1" t="s">
         <v>0</v>
@@ -3251,19 +3390,19 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -3271,7 +3410,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0015B3CF-9070-4AB0-A8B1-769A8784C11C}">
   <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -3290,34 +3429,34 @@
         <v>1</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="G1" t="s">
+        <v>204</v>
+      </c>
+      <c r="H1" t="s">
         <v>206</v>
       </c>
-      <c r="H1" t="s">
-        <v>208</v>
-      </c>
       <c r="I1" t="s">
+        <v>207</v>
+      </c>
+      <c r="J1" t="s">
         <v>209</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>211</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>213</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
+        <v>214</v>
+      </c>
+      <c r="N1" t="s">
         <v>215</v>
-      </c>
-      <c r="M1" t="s">
-        <v>216</v>
-      </c>
-      <c r="N1" t="s">
-        <v>217</v>
       </c>
       <c r="O1" t="s">
         <v>0</v>
@@ -3325,19 +3464,19 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="1"/>
       <c r="G2" s="6"/>
       <c r="H2" s="7"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="11"/>
-      <c r="N2" s="10"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="8"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3345,10 +3484,15 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B67CCBB0-59C0-48CB-A87A-0B0C4F1FD065}">
   <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="28.453125" customWidth="1"/>
+    <col min="2" max="2" width="16.26953125" customWidth="1"/>
+    <col min="3" max="3" width="21.81640625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
@@ -3364,46 +3508,41 @@
         <v>1</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="G1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
-        <v>122</v>
+      <c r="A2" s="1" t="s">
+        <v>200</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>121</v>
+        <v>201</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>123</v>
+        <v>202</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" xr:uid="{BF67F2E5-ACB9-4272-AE60-74BC4C8AE484}"/>
-    <hyperlink ref="A2" r:id="rId2" xr:uid="{8E026CDC-0730-4A08-BD6A-9CFBA157B452}"/>
-    <hyperlink ref="C2" r:id="rId3" xr:uid="{65D881A0-E022-427D-A2CD-B9A87CDED0BE}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B601A09D-93F0-4AB8-824B-DB778A997F8A}">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -3416,10 +3555,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E1" t="s">
         <v>0</v>
@@ -3427,16 +3566,16 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C2" t="s">
         <v>49</v>
       </c>
       <c r="D2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -3447,7 +3586,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3D33E6F-A6B1-4616-954D-27E1D6F16508}">
   <dimension ref="A1:J16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -3472,19 +3611,19 @@
         <v>1</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="G1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I1" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="J1" t="s">
         <v>0</v>
@@ -3492,25 +3631,25 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E2" t="s">
         <v>49</v>
       </c>
       <c r="F2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="G2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H2" t="s">
         <v>49</v>
@@ -3521,22 +3660,22 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G3" t="s">
         <v>49</v>
@@ -3545,76 +3684,76 @@
         <v>27</v>
       </c>
       <c r="I3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>39</v>
       </c>
       <c r="E4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F4" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="G4" t="s">
         <v>27</v>
       </c>
       <c r="H4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E5" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F5" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G5" t="s">
         <v>47</v>
       </c>
       <c r="H5" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="I5" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>47</v>
@@ -3623,10 +3762,10 @@
         <v>49</v>
       </c>
       <c r="F6" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="G6" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="H6" t="s">
         <v>59</v>
@@ -3637,57 +3776,57 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E7" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F7" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G7" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H7" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="I7" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>59</v>
       </c>
       <c r="E8" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F8" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="G8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H8" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="I8" t="s">
         <v>47</v>
@@ -3695,13 +3834,13 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>27</v>
@@ -3710,13 +3849,13 @@
         <v>59</v>
       </c>
       <c r="F9" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G9" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="H9" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="I9" t="s">
         <v>59</v>
@@ -3724,42 +3863,42 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E10" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F10" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="G10" t="s">
         <v>47</v>
       </c>
       <c r="H10" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="I10" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>43</v>
@@ -3768,85 +3907,85 @@
         <v>45</v>
       </c>
       <c r="F11" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G11" t="s">
         <v>49</v>
       </c>
       <c r="H11" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="I11" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E12" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F12" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="G12" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="H12" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="I12" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E13" t="s">
         <v>49</v>
       </c>
       <c r="F13" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="G13" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H13" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I13" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D14" t="s">
         <v>42</v>
@@ -3855,7 +3994,7 @@
         <v>43</v>
       </c>
       <c r="F14" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="G14" t="s">
         <v>49</v>
@@ -3864,65 +4003,65 @@
         <v>59</v>
       </c>
       <c r="I14" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>49</v>
       </c>
       <c r="E15" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F15" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G15" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="H15" t="s">
         <v>27</v>
       </c>
       <c r="I15" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>41</v>
       </c>
       <c r="E16" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G16" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="H16" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I16" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
   </sheetData>
@@ -3930,7 +4069,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D2A165B-C0AE-450E-8DD8-0A7073A78BBC}">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -3949,7 +4088,7 @@
         <v>1</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F1" t="s">
         <v>0</v>
@@ -3957,13 +4096,13 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>49</v>
@@ -3977,7 +4116,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0097D35B-A3B5-43FF-807C-CC910EC043F4}">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -3999,7 +4138,7 @@
         <v>1</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F1" t="s">
         <v>0</v>
@@ -4007,16 +4146,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E2" t="s">
         <v>49</v>
@@ -6636,34 +6775,34 @@
         <v>1</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="G1" t="s">
+        <v>204</v>
+      </c>
+      <c r="H1" t="s">
         <v>206</v>
       </c>
-      <c r="H1" t="s">
-        <v>208</v>
-      </c>
       <c r="I1" t="s">
+        <v>207</v>
+      </c>
+      <c r="J1" t="s">
         <v>209</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>211</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>213</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
+        <v>214</v>
+      </c>
+      <c r="N1" t="s">
         <v>215</v>
-      </c>
-      <c r="M1" t="s">
-        <v>216</v>
-      </c>
-      <c r="N1" t="s">
-        <v>217</v>
       </c>
       <c r="O1" t="s">
         <v>0</v>
@@ -6671,54 +6810,54 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E2">
         <v>2</v>
       </c>
       <c r="F2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H2" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="9" t="s">
+      <c r="I2" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J2" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="J2" s="9" t="s">
+      <c r="K2" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L2" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M2" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="N2" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="K2" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L2" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M2" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N2" s="10" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="1" t="s">
@@ -6728,31 +6867,31 @@
         <v>2</v>
       </c>
       <c r="F3" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="I3" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J3" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="K3" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M3" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="N3" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="K3" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L3" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M3" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N3" s="10" t="s">
-        <v>214</v>
       </c>
       <c r="O3" t="s">
         <v>120</v>
@@ -6760,13 +6899,13 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>49</v>
@@ -6775,31 +6914,31 @@
         <v>3</v>
       </c>
       <c r="F4" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H4" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="I4" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J4" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="J4" s="9" t="s">
+      <c r="K4" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M4" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="N4" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="K4" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L4" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M4" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N4" s="10" t="s">
-        <v>214</v>
       </c>
       <c r="O4" t="s">
         <v>120</v>
@@ -6807,13 +6946,13 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>47</v>
@@ -6822,31 +6961,31 @@
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H5" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I5" s="9" t="s">
+      <c r="I5" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J5" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="J5" s="9" t="s">
+      <c r="K5" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M5" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="N5" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="K5" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L5" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M5" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N5" s="10" t="s">
-        <v>214</v>
       </c>
       <c r="O5" t="s">
         <v>120</v>
@@ -6854,46 +6993,46 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E6">
         <v>2</v>
       </c>
       <c r="F6" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H6" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I6" s="9" t="s">
+      <c r="I6" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J6" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="J6" s="9" t="s">
+      <c r="K6" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M6" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="N6" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="K6" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L6" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M6" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N6" s="10" t="s">
-        <v>214</v>
       </c>
       <c r="O6" t="s">
         <v>120</v>
@@ -6901,13 +7040,13 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>48</v>
@@ -6916,31 +7055,31 @@
         <v>3</v>
       </c>
       <c r="F7" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H7" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I7" s="9" t="s">
+      <c r="I7" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J7" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="J7" s="9" t="s">
+      <c r="K7" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M7" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="N7" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="K7" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L7" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M7" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N7" s="10" t="s">
-        <v>214</v>
       </c>
       <c r="O7" t="s">
         <v>120</v>
@@ -6948,46 +7087,46 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E8">
         <v>3</v>
       </c>
       <c r="F8" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H8" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I8" s="9" t="s">
+      <c r="I8" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J8" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="J8" s="9" t="s">
+      <c r="K8" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M8" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="N8" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="K8" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L8" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M8" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N8" s="10" t="s">
-        <v>214</v>
       </c>
       <c r="O8" t="s">
         <v>120</v>
@@ -6995,13 +7134,13 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>42</v>
@@ -7010,31 +7149,31 @@
         <v>4</v>
       </c>
       <c r="F9" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H9" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I9" s="9" t="s">
+      <c r="I9" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J9" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="J9" s="9" t="s">
+      <c r="K9" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M9" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="N9" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="K9" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L9" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M9" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N9" s="10" t="s">
-        <v>214</v>
       </c>
       <c r="O9" t="s">
         <v>120</v>
@@ -7042,46 +7181,46 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E10">
         <v>2</v>
       </c>
       <c r="F10" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H10" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I10" s="9" t="s">
+      <c r="I10" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J10" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="J10" s="9" t="s">
+      <c r="K10" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M10" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="N10" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="K10" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L10" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M10" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N10" s="10" t="s">
-        <v>214</v>
       </c>
       <c r="O10" t="s">
         <v>120</v>
@@ -7089,46 +7228,46 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E11">
         <v>1</v>
       </c>
       <c r="F11" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H11" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I11" s="9" t="s">
+      <c r="I11" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J11" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="J11" s="9" t="s">
+      <c r="K11" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M11" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="N11" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="K11" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L11" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M11" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N11" s="10" t="s">
-        <v>214</v>
       </c>
       <c r="O11" t="s">
         <v>120</v>
@@ -7136,13 +7275,13 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>87</v>
@@ -7151,31 +7290,31 @@
         <v>1</v>
       </c>
       <c r="F12" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H12" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I12" s="9" t="s">
+      <c r="I12" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J12" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="J12" s="9" t="s">
+      <c r="K12" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M12" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="N12" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="K12" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L12" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M12" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N12" s="10" t="s">
-        <v>214</v>
       </c>
       <c r="O12" t="s">
         <v>120</v>
@@ -7183,46 +7322,46 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E13">
         <v>3</v>
       </c>
       <c r="F13" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H13" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I13" s="9" t="s">
+      <c r="I13" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J13" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="J13" s="9" t="s">
+      <c r="K13" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L13" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M13" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="N13" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="K13" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L13" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M13" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N13" s="10" t="s">
-        <v>214</v>
       </c>
       <c r="O13" t="s">
         <v>120</v>
@@ -7230,46 +7369,46 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E14">
         <v>2</v>
       </c>
       <c r="F14" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H14" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I14" s="9" t="s">
+      <c r="I14" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J14" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="J14" s="9" t="s">
+      <c r="K14" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M14" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="N14" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="K14" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L14" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M14" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N14" s="10" t="s">
-        <v>214</v>
       </c>
       <c r="O14" t="s">
         <v>120</v>
@@ -7277,46 +7416,46 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E15">
         <v>1</v>
       </c>
       <c r="F15" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H15" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I15" s="9" t="s">
+      <c r="I15" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J15" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="J15" s="9" t="s">
+      <c r="K15" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M15" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="N15" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="K15" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L15" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M15" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N15" s="10" t="s">
-        <v>214</v>
       </c>
       <c r="O15" t="s">
         <v>120</v>
@@ -7324,46 +7463,46 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E16">
         <v>4</v>
       </c>
       <c r="F16" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H16" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I16" s="9" t="s">
+      <c r="I16" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J16" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="J16" s="9" t="s">
+      <c r="K16" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M16" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="N16" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="K16" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L16" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M16" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N16" s="10" t="s">
-        <v>214</v>
       </c>
       <c r="O16" t="s">
         <v>120</v>
@@ -7371,46 +7510,46 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E17">
         <v>5</v>
       </c>
       <c r="F17" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H17" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I17" s="9" t="s">
+      <c r="I17" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J17" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="J17" s="9" t="s">
+      <c r="K17" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M17" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="N17" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="K17" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L17" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M17" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N17" s="10" t="s">
-        <v>214</v>
       </c>
       <c r="O17" t="s">
         <v>120</v>
@@ -7418,46 +7557,46 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E18">
         <v>2</v>
       </c>
       <c r="F18" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H18" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I18" s="9" t="s">
+      <c r="I18" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J18" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="J18" s="9" t="s">
+      <c r="K18" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M18" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="N18" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="K18" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L18" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M18" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N18" s="10" t="s">
-        <v>214</v>
       </c>
       <c r="O18" t="s">
         <v>120</v>
@@ -7465,46 +7604,46 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E19">
         <v>1</v>
       </c>
       <c r="F19" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H19" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I19" s="9" t="s">
+      <c r="I19" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J19" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="J19" s="9" t="s">
+      <c r="K19" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M19" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="N19" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="K19" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L19" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M19" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N19" s="10" t="s">
-        <v>214</v>
       </c>
       <c r="O19" t="s">
         <v>120</v>
@@ -7512,46 +7651,46 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E20">
         <v>3</v>
       </c>
       <c r="F20" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H20" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I20" s="9" t="s">
+      <c r="I20" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J20" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="J20" s="9" t="s">
+      <c r="K20" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L20" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M20" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="N20" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="K20" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L20" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M20" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N20" s="10" t="s">
-        <v>214</v>
       </c>
       <c r="O20" t="s">
         <v>120</v>
@@ -7559,13 +7698,13 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>88</v>
@@ -7574,31 +7713,31 @@
         <v>2</v>
       </c>
       <c r="F21" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H21" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I21" s="9" t="s">
+      <c r="I21" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J21" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="J21" s="9" t="s">
+      <c r="K21" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L21" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M21" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="N21" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="K21" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L21" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M21" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N21" s="10" t="s">
-        <v>214</v>
       </c>
       <c r="O21" t="s">
         <v>120</v>
@@ -7606,46 +7745,46 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E22">
         <v>3</v>
       </c>
       <c r="F22" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H22" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I22" s="9" t="s">
+      <c r="I22" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J22" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="J22" s="9" t="s">
+      <c r="K22" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L22" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M22" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="N22" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="K22" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L22" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M22" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N22" s="10" t="s">
-        <v>214</v>
       </c>
       <c r="O22" t="s">
         <v>120</v>
@@ -7653,46 +7792,46 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E23">
         <v>2</v>
       </c>
       <c r="F23" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H23" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I23" s="9" t="s">
+      <c r="I23" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J23" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="J23" s="9" t="s">
+      <c r="K23" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L23" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M23" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="N23" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="K23" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L23" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M23" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N23" s="10" t="s">
-        <v>214</v>
       </c>
       <c r="O23" t="s">
         <v>120</v>
@@ -7700,46 +7839,46 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E24">
         <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H24" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I24" s="9" t="s">
+      <c r="I24" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J24" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="J24" s="9" t="s">
+      <c r="K24" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L24" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M24" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="N24" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="K24" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L24" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M24" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N24" s="10" t="s">
-        <v>214</v>
       </c>
       <c r="O24" t="s">
         <v>120</v>
@@ -7747,46 +7886,46 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E25">
         <v>4</v>
       </c>
       <c r="F25" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H25" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I25" s="9" t="s">
+      <c r="I25" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J25" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="J25" s="9" t="s">
+      <c r="K25" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L25" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M25" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="N25" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="K25" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L25" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M25" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N25" s="10" t="s">
-        <v>214</v>
       </c>
       <c r="O25" t="s">
         <v>120</v>
@@ -7794,46 +7933,46 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E26">
         <v>2</v>
       </c>
       <c r="F26" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H26" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I26" s="9" t="s">
+      <c r="I26" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J26" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="J26" s="9" t="s">
+      <c r="K26" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L26" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M26" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="N26" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="K26" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L26" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M26" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N26" s="10" t="s">
-        <v>214</v>
       </c>
       <c r="O26" t="s">
         <v>120</v>
@@ -7841,46 +7980,46 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E27">
         <v>4</v>
       </c>
       <c r="F27" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H27" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I27" s="9" t="s">
+      <c r="I27" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J27" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="J27" s="9" t="s">
+      <c r="K27" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L27" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M27" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="N27" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="K27" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L27" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M27" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N27" s="10" t="s">
-        <v>214</v>
       </c>
       <c r="O27" t="s">
         <v>120</v>
@@ -7888,46 +8027,46 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E28">
         <v>3</v>
       </c>
       <c r="F28" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H28" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I28" s="9" t="s">
+      <c r="I28" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J28" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="J28" s="9" t="s">
+      <c r="K28" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L28" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M28" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="N28" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="K28" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L28" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M28" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N28" s="10" t="s">
-        <v>214</v>
       </c>
       <c r="O28" t="s">
         <v>120</v>
@@ -7935,46 +8074,46 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E29">
         <v>1</v>
       </c>
       <c r="F29" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H29" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I29" s="9" t="s">
+      <c r="I29" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J29" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="J29" s="9" t="s">
+      <c r="K29" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L29" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M29" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="N29" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="K29" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L29" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M29" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N29" s="10" t="s">
-        <v>214</v>
       </c>
       <c r="O29" t="s">
         <v>120</v>
@@ -7982,46 +8121,46 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E30">
         <v>5</v>
       </c>
       <c r="F30" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H30" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I30" s="9" t="s">
+      <c r="I30" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J30" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="J30" s="9" t="s">
+      <c r="K30" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L30" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M30" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="N30" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="K30" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L30" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M30" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N30" s="10" t="s">
-        <v>214</v>
       </c>
       <c r="O30" t="s">
         <v>120</v>
@@ -8029,46 +8168,46 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E31">
         <v>3</v>
       </c>
       <c r="F31" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H31" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I31" s="9" t="s">
+      <c r="I31" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J31" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="J31" s="9" t="s">
+      <c r="K31" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L31" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M31" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="N31" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="K31" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L31" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M31" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N31" s="10" t="s">
-        <v>214</v>
       </c>
       <c r="O31" t="s">
         <v>120</v>
@@ -8076,46 +8215,46 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E32">
         <v>4</v>
       </c>
       <c r="F32" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H32" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I32" s="9" t="s">
+      <c r="I32" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J32" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="J32" s="9" t="s">
+      <c r="K32" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L32" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M32" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="N32" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="K32" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L32" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M32" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N32" s="10" t="s">
-        <v>214</v>
       </c>
       <c r="O32" t="s">
         <v>120</v>
@@ -8123,46 +8262,46 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E33">
         <v>2</v>
       </c>
       <c r="F33" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H33" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I33" s="9" t="s">
+      <c r="I33" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J33" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="J33" s="9" t="s">
+      <c r="K33" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L33" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M33" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="N33" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="K33" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L33" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M33" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N33" s="10" t="s">
-        <v>214</v>
       </c>
       <c r="O33" t="s">
         <v>120</v>
@@ -8170,46 +8309,46 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E34">
         <v>1</v>
       </c>
       <c r="F34" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H34" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I34" s="9" t="s">
+      <c r="I34" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J34" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="J34" s="9" t="s">
+      <c r="K34" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L34" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M34" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="N34" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="K34" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L34" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M34" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N34" s="10" t="s">
-        <v>214</v>
       </c>
       <c r="O34" t="s">
         <v>120</v>
@@ -8217,46 +8356,46 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E35">
         <v>3</v>
       </c>
       <c r="F35" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H35" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I35" s="9" t="s">
+      <c r="I35" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J35" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="J35" s="9" t="s">
+      <c r="K35" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L35" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M35" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="N35" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="K35" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L35" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M35" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N35" s="10" t="s">
-        <v>214</v>
       </c>
       <c r="O35" t="s">
         <v>120</v>
@@ -8264,46 +8403,46 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E36">
         <v>1</v>
       </c>
       <c r="F36" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H36" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I36" s="9" t="s">
+      <c r="I36" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J36" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="J36" s="9" t="s">
+      <c r="K36" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L36" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M36" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="N36" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="K36" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L36" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M36" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N36" s="10" t="s">
-        <v>214</v>
       </c>
       <c r="O36" t="s">
         <v>120</v>
@@ -8311,46 +8450,46 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E37">
         <v>3</v>
       </c>
       <c r="F37" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H37" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I37" s="9" t="s">
+      <c r="I37" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J37" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="J37" s="9" t="s">
+      <c r="K37" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L37" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M37" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="N37" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="K37" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L37" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M37" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N37" s="10" t="s">
-        <v>214</v>
       </c>
       <c r="O37" t="s">
         <v>120</v>
@@ -8358,46 +8497,46 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E38">
         <v>4</v>
       </c>
       <c r="F38" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H38" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I38" s="9" t="s">
+      <c r="I38" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J38" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="J38" s="9" t="s">
+      <c r="K38" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L38" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M38" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="N38" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="K38" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L38" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M38" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N38" s="10" t="s">
-        <v>214</v>
       </c>
       <c r="O38" t="s">
         <v>120</v>
@@ -8405,46 +8544,46 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E39">
         <v>5</v>
       </c>
       <c r="F39" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H39" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I39" s="9" t="s">
+      <c r="I39" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J39" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="J39" s="9" t="s">
+      <c r="K39" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L39" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M39" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="N39" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="K39" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L39" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M39" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N39" s="10" t="s">
-        <v>214</v>
       </c>
       <c r="O39" t="s">
         <v>120</v>
@@ -8452,46 +8591,46 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E40">
         <v>3</v>
       </c>
       <c r="F40" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H40" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I40" s="9" t="s">
+      <c r="I40" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J40" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="J40" s="9" t="s">
+      <c r="K40" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L40" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M40" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="N40" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="K40" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L40" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M40" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N40" s="10" t="s">
-        <v>214</v>
       </c>
       <c r="O40" t="s">
         <v>120</v>
@@ -8499,46 +8638,46 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E41">
         <v>2</v>
       </c>
       <c r="F41" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H41" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I41" s="9" t="s">
+      <c r="I41" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J41" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="J41" s="9" t="s">
+      <c r="K41" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L41" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M41" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="N41" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="K41" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L41" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M41" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N41" s="10" t="s">
-        <v>214</v>
       </c>
       <c r="O41" t="s">
         <v>120</v>
@@ -8546,46 +8685,46 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E42">
         <v>1</v>
       </c>
       <c r="F42" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H42" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I42" s="9" t="s">
+      <c r="I42" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J42" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="J42" s="9" t="s">
+      <c r="K42" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L42" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M42" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="N42" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="K42" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L42" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M42" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N42" s="10" t="s">
-        <v>214</v>
       </c>
       <c r="O42" t="s">
         <v>120</v>
@@ -8593,46 +8732,46 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E43">
         <v>3</v>
       </c>
       <c r="F43" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H43" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I43" s="9" t="s">
+      <c r="I43" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J43" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="J43" s="9" t="s">
+      <c r="K43" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L43" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M43" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="N43" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="K43" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L43" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M43" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N43" s="10" t="s">
-        <v>214</v>
       </c>
       <c r="O43" t="s">
         <v>120</v>
@@ -8640,46 +8779,46 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E44">
         <v>4</v>
       </c>
       <c r="F44" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H44" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I44" s="9" t="s">
+      <c r="I44" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J44" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="J44" s="9" t="s">
+      <c r="K44" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L44" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M44" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="N44" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="K44" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L44" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M44" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N44" s="10" t="s">
-        <v>214</v>
       </c>
       <c r="O44" t="s">
         <v>120</v>
@@ -8687,13 +8826,13 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>59</v>
@@ -8702,31 +8841,31 @@
         <v>5</v>
       </c>
       <c r="F45" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H45" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I45" s="9" t="s">
+      <c r="I45" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J45" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="J45" s="9" t="s">
+      <c r="K45" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L45" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M45" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="N45" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="K45" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L45" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M45" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N45" s="10" t="s">
-        <v>214</v>
       </c>
       <c r="O45" t="s">
         <v>120</v>
@@ -8734,46 +8873,46 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E46">
         <v>6</v>
       </c>
       <c r="F46" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H46" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I46" s="9" t="s">
+      <c r="I46" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J46" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="J46" s="9" t="s">
+      <c r="K46" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L46" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M46" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="N46" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="K46" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L46" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M46" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N46" s="10" t="s">
-        <v>214</v>
       </c>
       <c r="O46" t="s">
         <v>120</v>
@@ -8781,46 +8920,46 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E47">
         <v>3</v>
       </c>
       <c r="F47" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H47" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I47" s="9" t="s">
+      <c r="I47" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J47" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="J47" s="9" t="s">
+      <c r="K47" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L47" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M47" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="N47" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="K47" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L47" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M47" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N47" s="10" t="s">
-        <v>214</v>
       </c>
       <c r="O47" t="s">
         <v>120</v>
@@ -8828,13 +8967,13 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>41</v>
@@ -8843,31 +8982,31 @@
         <v>2</v>
       </c>
       <c r="F48" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H48" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I48" s="9" t="s">
+      <c r="I48" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J48" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="J48" s="9" t="s">
+      <c r="K48" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L48" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M48" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="N48" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="K48" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L48" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M48" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N48" s="10" t="s">
-        <v>214</v>
       </c>
       <c r="O48" t="s">
         <v>120</v>
@@ -8875,13 +9014,13 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>45</v>
@@ -8890,31 +9029,31 @@
         <v>1</v>
       </c>
       <c r="F49" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H49" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I49" s="9" t="s">
+      <c r="I49" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J49" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="J49" s="9" t="s">
+      <c r="K49" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L49" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M49" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="N49" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="K49" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L49" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M49" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N49" s="10" t="s">
-        <v>214</v>
       </c>
       <c r="O49" t="s">
         <v>120</v>
@@ -8922,13 +9061,13 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>58</v>
@@ -8937,31 +9076,31 @@
         <v>2</v>
       </c>
       <c r="F50" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H50" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I50" s="9" t="s">
+      <c r="I50" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J50" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="J50" s="9" t="s">
+      <c r="K50" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L50" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M50" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="N50" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="K50" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L50" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M50" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N50" s="10" t="s">
-        <v>214</v>
       </c>
       <c r="O50" t="s">
         <v>120</v>
@@ -8969,13 +9108,13 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D51" t="s">
         <v>95</v>
@@ -8984,31 +9123,31 @@
         <v>1</v>
       </c>
       <c r="F51" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G51" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H51" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I51" s="9" t="s">
+      <c r="I51" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J51" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="J51" s="9" t="s">
+      <c r="K51" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L51" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M51" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="N51" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="K51" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L51" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M51" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N51" s="10" t="s">
-        <v>214</v>
       </c>
       <c r="O51" t="s">
         <v>120</v>
@@ -9047,34 +9186,34 @@
         <v>1</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="G1" t="s">
+        <v>204</v>
+      </c>
+      <c r="H1" t="s">
         <v>206</v>
       </c>
-      <c r="H1" t="s">
-        <v>208</v>
-      </c>
       <c r="I1" t="s">
+        <v>207</v>
+      </c>
+      <c r="J1" t="s">
         <v>209</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>211</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>213</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
+        <v>214</v>
+      </c>
+      <c r="N1" t="s">
         <v>215</v>
-      </c>
-      <c r="M1" t="s">
-        <v>216</v>
-      </c>
-      <c r="N1" t="s">
-        <v>217</v>
       </c>
       <c r="O1" t="s">
         <v>0</v>
@@ -9082,90 +9221,90 @@
     </row>
     <row r="2" spans="1:15" ht="58" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E2">
         <v>2</v>
       </c>
       <c r="F2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H2" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="9" t="s">
+      <c r="I2" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J2" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="J2" s="9" t="s">
+      <c r="K2" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L2" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M2" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="N2" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="K2" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L2" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M2" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N2" s="10" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="58" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E3">
         <v>3</v>
       </c>
       <c r="F3" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="I3" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J3" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="K3" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M3" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="N3" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="K3" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L3" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M3" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N3" s="10" t="s">
-        <v>214</v>
       </c>
       <c r="O3" t="s">
         <v>120</v>
@@ -9173,13 +9312,13 @@
     </row>
     <row r="4" spans="1:15" ht="58" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>49</v>
@@ -9188,31 +9327,31 @@
         <v>3</v>
       </c>
       <c r="F4" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H4" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="I4" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J4" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="J4" s="9" t="s">
+      <c r="K4" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M4" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="N4" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="K4" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L4" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M4" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N4" s="10" t="s">
-        <v>214</v>
       </c>
       <c r="O4" t="s">
         <v>120</v>
@@ -9220,46 +9359,46 @@
     </row>
     <row r="5" spans="1:15" ht="58" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E5">
         <v>4</v>
       </c>
       <c r="F5" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H5" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I5" s="9" t="s">
+      <c r="I5" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J5" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="J5" s="9" t="s">
+      <c r="K5" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M5" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="N5" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="K5" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L5" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M5" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N5" s="10" t="s">
-        <v>214</v>
       </c>
       <c r="O5" t="s">
         <v>120</v>
@@ -9267,13 +9406,13 @@
     </row>
     <row r="6" spans="1:15" ht="58" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>43</v>
@@ -9282,31 +9421,31 @@
         <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H6" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I6" s="9" t="s">
+      <c r="I6" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J6" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="J6" s="9" t="s">
+      <c r="K6" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M6" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="N6" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="K6" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L6" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M6" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N6" s="10" t="s">
-        <v>214</v>
       </c>
       <c r="O6" t="s">
         <v>120</v>
@@ -9325,8 +9464,122 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0D47BAB-B941-4967-BD8D-FC98615724A1}">
+  <dimension ref="A1:O2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="32.26953125" customWidth="1"/>
+    <col min="2" max="2" width="19.90625" customWidth="1"/>
+    <col min="3" max="3" width="19.54296875" customWidth="1"/>
+    <col min="6" max="6" width="17.26953125" customWidth="1"/>
+    <col min="7" max="7" width="15.7265625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="F1" t="s">
+        <v>203</v>
+      </c>
+      <c r="G1" t="s">
+        <v>204</v>
+      </c>
+      <c r="H1" t="s">
+        <v>206</v>
+      </c>
+      <c r="I1" t="s">
+        <v>207</v>
+      </c>
+      <c r="J1" t="s">
+        <v>209</v>
+      </c>
+      <c r="K1" t="s">
+        <v>211</v>
+      </c>
+      <c r="L1" t="s">
+        <v>213</v>
+      </c>
+      <c r="M1" t="s">
+        <v>214</v>
+      </c>
+      <c r="N1" t="s">
+        <v>215</v>
+      </c>
+      <c r="O1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="58" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>251</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2" t="s">
+        <v>205</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="K2" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L2" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M2" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="N2" s="9" t="s">
+        <v>212</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="M2" r:id="rId1" xr:uid="{0C70E96E-DDE1-4C4A-B987-4F231DBBF744}"/>
+    <hyperlink ref="A2" r:id="rId2" xr:uid="{1CD4CE66-DBA1-4FBC-B400-F966D5302409}"/>
+    <hyperlink ref="C2" r:id="rId3" xr:uid="{A74A9176-C166-448E-8BA5-CFEB269DD879}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId4"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1F3EEA5-DCC3-4074-B026-57499537C17E}">
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="21.36328125" customWidth="1"/>
@@ -9336,7 +9589,7 @@
     <col min="12" max="12" width="20.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -9350,71 +9603,76 @@
         <v>1</v>
       </c>
       <c r="E1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F1" t="s">
+        <v>231</v>
+      </c>
+      <c r="G1" t="s">
+        <v>232</v>
+      </c>
+      <c r="H1" t="s">
         <v>233</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>234</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" s="11" t="s">
         <v>235</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>236</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="L1" t="s">
         <v>237</v>
-      </c>
-      <c r="K1" t="s">
-        <v>238</v>
-      </c>
-      <c r="L1" t="s">
-        <v>239</v>
       </c>
       <c r="M1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:14" ht="16" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="C2" s="13" t="s">
-        <v>204</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="F2" t="s">
         <v>241</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="G2" s="13" t="s">
         <v>242</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" s="14">
+        <v>1</v>
+      </c>
+      <c r="I2" s="14">
+        <v>10</v>
+      </c>
+      <c r="J2" s="14" t="s">
         <v>243</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="K2" s="14" t="s">
         <v>244</v>
       </c>
-      <c r="H2" s="15">
-        <v>1</v>
-      </c>
-      <c r="I2" s="15">
-        <v>2</v>
-      </c>
-      <c r="J2" s="15" t="s">
+      <c r="L2" s="14" t="s">
         <v>245</v>
       </c>
-      <c r="K2" s="15" t="s">
-        <v>246</v>
-      </c>
-      <c r="L2" s="15" t="s">
+      <c r="M2" s="14"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N8" t="s">
         <v>247</v>
       </c>
-      <c r="M2" s="15"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -9425,12 +9683,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28E34583-02BB-49FD-9732-540EBD790FDF}">
   <dimension ref="A1:M2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
+    <col min="2" max="2" width="19.81640625" customWidth="1"/>
     <col min="6" max="6" width="15.81640625" customWidth="1"/>
+    <col min="8" max="8" width="25.54296875" customWidth="1"/>
     <col min="11" max="11" width="17.90625" customWidth="1"/>
     <col min="12" max="12" width="25.36328125" customWidth="1"/>
   </cols>
@@ -9446,28 +9706,28 @@
         <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F1" t="s">
+        <v>232</v>
+      </c>
+      <c r="G1" t="s">
         <v>233</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>234</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" s="11" t="s">
         <v>235</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>236</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="K1" t="s">
         <v>237</v>
-      </c>
-      <c r="J1" t="s">
-        <v>238</v>
-      </c>
-      <c r="K1" t="s">
-        <v>239</v>
       </c>
       <c r="L1" t="s">
         <v>2</v>
@@ -9478,40 +9738,40 @@
     </row>
     <row r="2" spans="1:13" ht="16" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="B2" s="13" t="s">
-        <v>204</v>
+        <v>201</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>202</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>249</v>
       </c>
       <c r="E2" t="s">
+        <v>241</v>
+      </c>
+      <c r="F2" s="13" t="s">
+        <v>246</v>
+      </c>
+      <c r="G2" s="14">
+        <v>1</v>
+      </c>
+      <c r="H2" s="14">
+        <v>1</v>
+      </c>
+      <c r="I2" s="14" t="s">
         <v>243</v>
       </c>
-      <c r="F2" s="14" t="s">
-        <v>248</v>
-      </c>
-      <c r="G2" s="15">
-        <v>1</v>
-      </c>
-      <c r="H2" s="15">
-        <v>2</v>
-      </c>
-      <c r="I2" s="15" t="s">
+      <c r="J2" s="14" t="s">
+        <v>244</v>
+      </c>
+      <c r="K2" s="14" t="s">
         <v>245</v>
       </c>
-      <c r="J2" s="15" t="s">
-        <v>246</v>
-      </c>
-      <c r="K2" s="15" t="s">
-        <v>247</v>
-      </c>
       <c r="L2" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
   </sheetData>
@@ -9521,108 +9781,4 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1594D560-AC0A-434C-82B6-21B802CD2CA5}">
-  <dimension ref="A1:O2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="F1" t="s">
-        <v>205</v>
-      </c>
-      <c r="G1" t="s">
-        <v>206</v>
-      </c>
-      <c r="H1" t="s">
-        <v>208</v>
-      </c>
-      <c r="I1" t="s">
-        <v>209</v>
-      </c>
-      <c r="J1" t="s">
-        <v>211</v>
-      </c>
-      <c r="K1" t="s">
-        <v>213</v>
-      </c>
-      <c r="L1" t="s">
-        <v>215</v>
-      </c>
-      <c r="M1" t="s">
-        <v>216</v>
-      </c>
-      <c r="N1" t="s">
-        <v>217</v>
-      </c>
-      <c r="O1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" ht="58" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2" t="s">
-        <v>207</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="J2" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="K2" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="L2" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M2" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N2" s="10" t="s">
-        <v>214</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="M2" r:id="rId1" xr:uid="{7F7B95CD-2341-4E68-B495-28B6BB9649F5}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/src/test/resources/testdata/HotelsScripts_Skytravelers.xlsx
+++ b/src/test/resources/testdata/HotelsScripts_Skytravelers.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AutomationScripts\TripGain_TestCases\src\test\resources\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{013B0A78-CF6B-4345-8A79-B1C4E3B87A0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5CD9A0F-4D62-4522-88CA-14125B5B33CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="11" activeTab="14" xr2:uid="{512D99D7-B637-4054-871A-E0DB86511A8A}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="12" activeTab="16" xr2:uid="{512D99D7-B637-4054-871A-E0DB86511A8A}"/>
   </bookViews>
   <sheets>
     <sheet name="TCHO_1" sheetId="2" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2077" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2091" uniqueCount="256">
   <si>
     <t>TestRun</t>
   </si>
@@ -3686,6 +3686,9 @@
       <c r="I3" t="s">
         <v>124</v>
       </c>
+      <c r="J3" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
@@ -3715,6 +3718,9 @@
       <c r="I4" t="s">
         <v>123</v>
       </c>
+      <c r="J4" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
@@ -3744,6 +3750,9 @@
       <c r="I5" t="s">
         <v>153</v>
       </c>
+      <c r="J5" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
@@ -3773,6 +3782,9 @@
       <c r="I6" t="s">
         <v>49</v>
       </c>
+      <c r="J6" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
@@ -3802,6 +3814,9 @@
       <c r="I7" t="s">
         <v>199</v>
       </c>
+      <c r="J7" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
@@ -3831,6 +3846,9 @@
       <c r="I8" t="s">
         <v>47</v>
       </c>
+      <c r="J8" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
@@ -3860,6 +3878,9 @@
       <c r="I9" t="s">
         <v>59</v>
       </c>
+      <c r="J9" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
@@ -3889,6 +3910,9 @@
       <c r="I10" t="s">
         <v>194</v>
       </c>
+      <c r="J10" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
@@ -3918,6 +3942,9 @@
       <c r="I11" t="s">
         <v>195</v>
       </c>
+      <c r="J11" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
@@ -3947,6 +3974,9 @@
       <c r="I12" t="s">
         <v>138</v>
       </c>
+      <c r="J12" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
@@ -3976,6 +4006,9 @@
       <c r="I13" t="s">
         <v>192</v>
       </c>
+      <c r="J13" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
@@ -4005,6 +4038,9 @@
       <c r="I14" t="s">
         <v>197</v>
       </c>
+      <c r="J14" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
@@ -4034,6 +4070,9 @@
       <c r="I15" t="s">
         <v>152</v>
       </c>
+      <c r="J15" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
@@ -4062,6 +4101,9 @@
       </c>
       <c r="I16" t="s">
         <v>196</v>
+      </c>
+      <c r="J16" t="s">
+        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/testdata/HotelsScripts_Skytravelers.xlsx
+++ b/src/test/resources/testdata/HotelsScripts_Skytravelers.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AutomationScripts\TripGain_TestCases\src\test\resources\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5CD9A0F-4D62-4522-88CA-14125B5B33CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3862DD60-49AE-415E-AA6F-7652F910D716}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="12" activeTab="16" xr2:uid="{512D99D7-B637-4054-871A-E0DB86511A8A}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="4" activeTab="4" xr2:uid="{512D99D7-B637-4054-871A-E0DB86511A8A}"/>
   </bookViews>
   <sheets>
     <sheet name="TCHO_1" sheetId="2" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2091" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2092" uniqueCount="256">
   <si>
     <t>TestRun</t>
   </si>
@@ -3655,7 +3655,7 @@
         <v>49</v>
       </c>
       <c r="I2" t="s">
-        <v>27</v>
+        <v>153</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
@@ -6888,7 +6888,7 @@
         <v>201</v>
       </c>
       <c r="M2" s="10" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="N2" s="9" t="s">
         <v>212</v>
@@ -6901,7 +6901,9 @@
       <c r="B3" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="C3" s="2"/>
+      <c r="C3" s="2" t="s">
+        <v>202</v>
+      </c>
       <c r="D3" s="1" t="s">
         <v>39</v>
       </c>
@@ -6930,7 +6932,7 @@
         <v>201</v>
       </c>
       <c r="M3" s="10" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="N3" s="9" t="s">
         <v>212</v>
@@ -6977,7 +6979,7 @@
         <v>201</v>
       </c>
       <c r="M4" s="10" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="N4" s="9" t="s">
         <v>212</v>
@@ -7024,7 +7026,7 @@
         <v>201</v>
       </c>
       <c r="M5" s="10" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="N5" s="9" t="s">
         <v>212</v>
@@ -7071,7 +7073,7 @@
         <v>201</v>
       </c>
       <c r="M6" s="10" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="N6" s="9" t="s">
         <v>212</v>
@@ -7118,7 +7120,7 @@
         <v>201</v>
       </c>
       <c r="M7" s="10" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="N7" s="9" t="s">
         <v>212</v>
@@ -7165,7 +7167,7 @@
         <v>201</v>
       </c>
       <c r="M8" s="10" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="N8" s="9" t="s">
         <v>212</v>
@@ -7212,7 +7214,7 @@
         <v>201</v>
       </c>
       <c r="M9" s="10" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="N9" s="9" t="s">
         <v>212</v>
@@ -7259,7 +7261,7 @@
         <v>201</v>
       </c>
       <c r="M10" s="10" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="N10" s="9" t="s">
         <v>212</v>
@@ -7306,7 +7308,7 @@
         <v>201</v>
       </c>
       <c r="M11" s="10" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="N11" s="9" t="s">
         <v>212</v>
@@ -7353,7 +7355,7 @@
         <v>201</v>
       </c>
       <c r="M12" s="10" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="N12" s="9" t="s">
         <v>212</v>
@@ -7400,7 +7402,7 @@
         <v>201</v>
       </c>
       <c r="M13" s="10" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="N13" s="9" t="s">
         <v>212</v>
@@ -7447,7 +7449,7 @@
         <v>201</v>
       </c>
       <c r="M14" s="10" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="N14" s="9" t="s">
         <v>212</v>
@@ -7494,7 +7496,7 @@
         <v>201</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="N15" s="9" t="s">
         <v>212</v>
@@ -7541,7 +7543,7 @@
         <v>201</v>
       </c>
       <c r="M16" s="10" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="N16" s="9" t="s">
         <v>212</v>
@@ -7588,7 +7590,7 @@
         <v>201</v>
       </c>
       <c r="M17" s="10" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="N17" s="9" t="s">
         <v>212</v>
@@ -7635,7 +7637,7 @@
         <v>201</v>
       </c>
       <c r="M18" s="10" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="N18" s="9" t="s">
         <v>212</v>
@@ -7682,7 +7684,7 @@
         <v>201</v>
       </c>
       <c r="M19" s="10" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="N19" s="9" t="s">
         <v>212</v>
@@ -7729,7 +7731,7 @@
         <v>201</v>
       </c>
       <c r="M20" s="10" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="N20" s="9" t="s">
         <v>212</v>
@@ -7776,7 +7778,7 @@
         <v>201</v>
       </c>
       <c r="M21" s="10" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="N21" s="9" t="s">
         <v>212</v>
@@ -7823,7 +7825,7 @@
         <v>201</v>
       </c>
       <c r="M22" s="10" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="N22" s="9" t="s">
         <v>212</v>
@@ -7870,7 +7872,7 @@
         <v>201</v>
       </c>
       <c r="M23" s="10" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="N23" s="9" t="s">
         <v>212</v>
@@ -7917,7 +7919,7 @@
         <v>201</v>
       </c>
       <c r="M24" s="10" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="N24" s="9" t="s">
         <v>212</v>
@@ -7964,7 +7966,7 @@
         <v>201</v>
       </c>
       <c r="M25" s="10" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="N25" s="9" t="s">
         <v>212</v>
@@ -8011,7 +8013,7 @@
         <v>201</v>
       </c>
       <c r="M26" s="10" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="N26" s="9" t="s">
         <v>212</v>
@@ -8058,7 +8060,7 @@
         <v>201</v>
       </c>
       <c r="M27" s="10" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="N27" s="9" t="s">
         <v>212</v>
@@ -8105,7 +8107,7 @@
         <v>201</v>
       </c>
       <c r="M28" s="10" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="N28" s="9" t="s">
         <v>212</v>
@@ -8152,7 +8154,7 @@
         <v>201</v>
       </c>
       <c r="M29" s="10" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="N29" s="9" t="s">
         <v>212</v>
@@ -8199,7 +8201,7 @@
         <v>201</v>
       </c>
       <c r="M30" s="10" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="N30" s="9" t="s">
         <v>212</v>
@@ -8246,7 +8248,7 @@
         <v>201</v>
       </c>
       <c r="M31" s="10" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="N31" s="9" t="s">
         <v>212</v>
@@ -8293,7 +8295,7 @@
         <v>201</v>
       </c>
       <c r="M32" s="10" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="N32" s="9" t="s">
         <v>212</v>
@@ -8340,7 +8342,7 @@
         <v>201</v>
       </c>
       <c r="M33" s="10" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="N33" s="9" t="s">
         <v>212</v>
@@ -8387,7 +8389,7 @@
         <v>201</v>
       </c>
       <c r="M34" s="10" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="N34" s="9" t="s">
         <v>212</v>
@@ -8434,7 +8436,7 @@
         <v>201</v>
       </c>
       <c r="M35" s="10" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="N35" s="9" t="s">
         <v>212</v>
@@ -8481,7 +8483,7 @@
         <v>201</v>
       </c>
       <c r="M36" s="10" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="N36" s="9" t="s">
         <v>212</v>
@@ -8528,7 +8530,7 @@
         <v>201</v>
       </c>
       <c r="M37" s="10" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="N37" s="9" t="s">
         <v>212</v>
@@ -8575,7 +8577,7 @@
         <v>201</v>
       </c>
       <c r="M38" s="10" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="N38" s="9" t="s">
         <v>212</v>
@@ -8622,7 +8624,7 @@
         <v>201</v>
       </c>
       <c r="M39" s="10" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="N39" s="9" t="s">
         <v>212</v>
@@ -8669,7 +8671,7 @@
         <v>201</v>
       </c>
       <c r="M40" s="10" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="N40" s="9" t="s">
         <v>212</v>
@@ -8716,7 +8718,7 @@
         <v>201</v>
       </c>
       <c r="M41" s="10" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="N41" s="9" t="s">
         <v>212</v>
@@ -8763,7 +8765,7 @@
         <v>201</v>
       </c>
       <c r="M42" s="10" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="N42" s="9" t="s">
         <v>212</v>
@@ -8810,7 +8812,7 @@
         <v>201</v>
       </c>
       <c r="M43" s="10" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="N43" s="9" t="s">
         <v>212</v>
@@ -8857,7 +8859,7 @@
         <v>201</v>
       </c>
       <c r="M44" s="10" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="N44" s="9" t="s">
         <v>212</v>
@@ -8904,7 +8906,7 @@
         <v>201</v>
       </c>
       <c r="M45" s="10" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="N45" s="9" t="s">
         <v>212</v>
@@ -8951,7 +8953,7 @@
         <v>201</v>
       </c>
       <c r="M46" s="10" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="N46" s="9" t="s">
         <v>212</v>
@@ -8998,7 +9000,7 @@
         <v>201</v>
       </c>
       <c r="M47" s="10" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="N47" s="9" t="s">
         <v>212</v>
@@ -9045,7 +9047,7 @@
         <v>201</v>
       </c>
       <c r="M48" s="10" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="N48" s="9" t="s">
         <v>212</v>
@@ -9092,7 +9094,7 @@
         <v>201</v>
       </c>
       <c r="M49" s="10" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="N49" s="9" t="s">
         <v>212</v>
@@ -9139,7 +9141,7 @@
         <v>201</v>
       </c>
       <c r="M50" s="10" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="N50" s="9" t="s">
         <v>212</v>
@@ -9186,7 +9188,7 @@
         <v>201</v>
       </c>
       <c r="M51" s="10" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="N51" s="9" t="s">
         <v>212</v>
@@ -9199,8 +9201,8 @@
   <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="M2" r:id="rId1" xr:uid="{CCA707E1-4567-4C38-B7DE-0422E4B7EFEF}"/>
-    <hyperlink ref="M3:M51" r:id="rId2" display="testfinanceadmin98@tripgain.com" xr:uid="{55372BF5-A41F-4C9E-9C8A-42BFEAD79DED}"/>
-    <hyperlink ref="B2" r:id="rId3" xr:uid="{793A0C57-0A27-44C4-84C9-EBFC97D3785B}"/>
+    <hyperlink ref="B2" r:id="rId2" xr:uid="{793A0C57-0A27-44C4-84C9-EBFC97D3785B}"/>
+    <hyperlink ref="M3:M51" r:id="rId3" display="testfinance98@tripgain.com" xr:uid="{EBA6D6CC-3EBF-4D24-8FE7-CC9FE457C2EA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
